--- a/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88012394-2260-4D52-9AC1-C84A6D174005}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B89B571-E7B3-45A2-ACB0-E4142807B9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="183">
   <si>
     <t>Anti-Dumping Duty : 2026</t>
   </si>
@@ -541,6 +541,36 @@
   </si>
   <si>
     <t>Seeks to impose anti-dumping duty on imports of Sulphenamides Accelerators originating in or exported from China for a period of 5 years</t>
+  </si>
+  <si>
+    <t>16/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to amend notification No. 64/2021-Customs (ADD), dated the 28th October, 2021 to extend the levy of anti dumping duty on "Seamless Tubes, Pipes and Hollow Profiles of Iron, Alloy or Non-Alloy Steel" originating in or exported from China PR, up to and inclusive of 27th January, 2027</t>
+  </si>
+  <si>
+    <t>15/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to continue anti dumping duty on imports of ‘Normal Butanol’ or ‘N-Butyl Alcohol’ originating in or exported from Malaysia, South Africa and United States of America for 5 years</t>
+  </si>
+  <si>
+    <t>14/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to provide for provisional assessment of of imports of 'Glufosinate and it salt' originating in or exported from People’s Republic of China pursuant to initiation of anti absorption investigation</t>
+  </si>
+  <si>
+    <t>13/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to provide for provisional assessment of of imports of 'Insoluble Sulphur' originating in or exported from People’s Republic of China pursuant to initiation of anti absorption investigation</t>
+  </si>
+  <si>
+    <t>17/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to extend anti dumping duty on imports of “Aceto Acetyl Derivatives of Aromatic Or Hetrocyclic Compounds” also known as “Arylides” originating in or exported from China PR till and inclusive of 13th January 2027</t>
   </si>
 </sst>
 </file>
@@ -572,7 +602,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -582,6 +612,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -598,7 +634,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -626,6 +662,13 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -907,12 +950,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
     <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="129.140625" style="4" customWidth="1"/>
+    <col min="3" max="3" width="155.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
@@ -932,134 +975,189 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="13">
+        <v>46213</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B7" s="13">
+        <v>46209</v>
+      </c>
+      <c r="C7" s="14" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="B9" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B10" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="7" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="8">
+      <c r="B11" s="8">
         <v>46192</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C11" s="6" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="B7" s="8">
+      <c r="B12" s="8">
         <v>46192</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C12" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B8" s="8">
+      <c r="B13" s="8">
         <v>46183</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C13" s="6" t="s">
         <v>168</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="9" t="s">
-        <v>163</v>
-      </c>
-      <c r="B9" s="10">
-        <v>46164</v>
-      </c>
-      <c r="C9" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="B10" s="10">
-        <v>46164</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="9" t="s">
-        <v>161</v>
-      </c>
-      <c r="B11" s="10">
-        <v>46161</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B12" s="10">
-        <v>46142</v>
-      </c>
-      <c r="C12" s="11" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="B13" s="10">
-        <v>46129</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="9" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B14" s="10">
-        <v>46120</v>
+        <v>46164</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
-        <v>153</v>
+        <v>165</v>
       </c>
       <c r="B15" s="10">
-        <v>46063</v>
+        <v>46164</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>154</v>
+        <v>166</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A16" s="9" t="s">
+        <v>161</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46161</v>
+      </c>
+      <c r="C16" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C17" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46129</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46120</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46063</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>149</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B21" s="10">
         <v>46030</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B22" s="10">
         <v>46024</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>152</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B89B571-E7B3-45A2-ACB0-E4142807B9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05675CE4-2CD1-4A73-9E64-688736573898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="185">
   <si>
     <t>Anti-Dumping Duty : 2026</t>
   </si>
@@ -571,6 +571,12 @@
   </si>
   <si>
     <t>Seeks to extend anti dumping duty on imports of “Aceto Acetyl Derivatives of Aromatic Or Hetrocyclic Compounds” also known as “Arylides” originating in or exported from China PR till and inclusive of 13th January 2027</t>
+  </si>
+  <si>
+    <t>18/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to impose anti-dumping duty on imports of "Low Ash Metallurgical Coke" originating in or exported from Australia, China PR, Colombia, Indonesia, Japan and Russia for a period of 5 years.</t>
   </si>
 </sst>
 </file>
@@ -602,7 +608,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -621,6 +627,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -634,7 +646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -668,6 +680,11 @@
     </xf>
     <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -950,7 +967,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -975,189 +992,200 @@
       </c>
     </row>
     <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B6" s="13">
-        <v>46213</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>182</v>
+      <c r="A6" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="B6" s="16">
+        <v>46230</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B7" s="13">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="C7" s="14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B8" s="13">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B9" s="13">
         <v>46206</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B10" s="13">
         <v>46206</v>
       </c>
       <c r="C10" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B11" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C11" s="14" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B11" s="8">
-        <v>46192</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="B12" s="8">
         <v>46192</v>
       </c>
       <c r="C12" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B13" s="8">
+        <v>46192</v>
+      </c>
+      <c r="C13" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B13" s="8">
+      <c r="B14" s="8">
         <v>46183</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C14" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="9" t="s">
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="B14" s="10">
-        <v>46164</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="B15" s="10">
         <v>46164</v>
       </c>
       <c r="C15" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B16" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C16" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B17" s="10">
         <v>46161</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C17" s="11" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B17" s="10">
-        <v>46142</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C18" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B19" s="10">
         <v>46129</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B20" s="10">
         <v>46120</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B21" s="10">
         <v>46063</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B21" s="10">
-        <v>46030</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B22" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C22" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B23" s="10">
         <v>46024</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>152</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05675CE4-2CD1-4A73-9E64-688736573898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BB3DC7-DC17-45E1-B5D8-4F9671E5BF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="187">
   <si>
     <t>Anti-Dumping Duty : 2026</t>
   </si>
@@ -577,6 +577,12 @@
   </si>
   <si>
     <t>Seeks to impose anti-dumping duty on imports of "Low Ash Metallurgical Coke" originating in or exported from Australia, China PR, Colombia, Indonesia, Japan and Russia for a period of 5 years.</t>
+  </si>
+  <si>
+    <t>19/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to extend anti dumping duty on imports of “Untreated Fumed Silica” originating in or exported from China PR till and inclusive of 10th February 2027.</t>
   </si>
 </sst>
 </file>
@@ -608,7 +614,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -633,6 +639,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -646,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -687,6 +699,12 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -967,7 +985,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -991,201 +1009,212 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+    <row r="6" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="B6" s="20">
+        <v>46234</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A7" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B7" s="16">
         <v>46230</v>
       </c>
-      <c r="C6" s="17" t="s">
+      <c r="C7" s="17" t="s">
         <v>184</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="B7" s="13">
-        <v>46213</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="B8" s="13">
-        <v>46209</v>
+        <v>46213</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B9" s="13">
-        <v>46206</v>
+        <v>46209</v>
       </c>
       <c r="C9" s="14" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B10" s="13">
         <v>46206</v>
       </c>
       <c r="C10" s="14" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B11" s="13">
         <v>46206</v>
       </c>
       <c r="C11" s="14" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A12" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B12" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C12" s="14" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B12" s="8">
-        <v>46192</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="B13" s="8">
         <v>46192</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="8">
+        <v>46192</v>
+      </c>
+      <c r="C14" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B15" s="8">
         <v>46183</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="9" t="s">
+    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="B15" s="10">
-        <v>46164</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="B16" s="10">
         <v>46164</v>
       </c>
       <c r="C16" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B17" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C17" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B18" s="10">
         <v>46161</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="10">
-        <v>46142</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B19" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C19" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A20" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B20" s="10">
         <v>46129</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B21" s="10">
         <v>46120</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B22" s="10">
         <v>46063</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B22" s="10">
-        <v>46030</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B23" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C23" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B24" s="10">
         <v>46024</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>152</v>
       </c>
     </row>

--- a/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74BB3DC7-DC17-45E1-B5D8-4F9671E5BF58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76921ED1-72D8-406B-89AB-E70A077B1ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="189">
   <si>
     <t>Anti-Dumping Duty : 2026</t>
   </si>
@@ -583,6 +583,12 @@
   </si>
   <si>
     <t>Seeks to extend anti dumping duty on imports of “Untreated Fumed Silica” originating in or exported from China PR till and inclusive of 10th February 2027.</t>
+  </si>
+  <si>
+    <t>20/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to continue anti dumping duty on imports of “Phthalic Anhydride” originating in or exported from China PR and Korea RP for a further period of 5 years pursuant to sunset review by DGTR.</t>
   </si>
 </sst>
 </file>
@@ -614,7 +620,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -645,6 +651,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC884F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -658,7 +676,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -704,13 +722,23 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFC884F2"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -985,7 +1013,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="28.7109375" customWidth="1"/>
@@ -993,12 +1021,12 @@
     <col min="3" max="3" width="155.5703125" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1009,212 +1037,231 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" s="21" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
+        <v>187</v>
+      </c>
+      <c r="B6" s="23">
+        <v>46239</v>
+      </c>
+      <c r="C6" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="21"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B7" s="20">
         <v>46234</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C7" s="19" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="D7" s="21"/>
+    </row>
+    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A8" s="15" t="s">
         <v>183</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B8" s="16">
         <v>46230</v>
       </c>
-      <c r="C7" s="17" t="s">
+      <c r="C8" s="17" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="12" t="s">
+      <c r="D8" s="21"/>
+    </row>
+    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A9" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="13">
+      <c r="B9" s="13">
         <v>46213</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C9" s="14" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+      <c r="D9" s="21"/>
+    </row>
+    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A10" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B10" s="13">
         <v>46209</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C10" s="14" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+      <c r="D10" s="21"/>
+    </row>
+    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A11" s="12" t="s">
         <v>175</v>
-      </c>
-      <c r="B10" s="13">
-        <v>46206</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
-        <v>177</v>
       </c>
       <c r="B11" s="13">
         <v>46206</v>
       </c>
       <c r="C11" s="14" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+        <v>176</v>
+      </c>
+      <c r="D11" s="21"/>
+    </row>
+    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B12" s="13">
         <v>46206</v>
       </c>
       <c r="C12" s="14" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="21"/>
+    </row>
+    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A13" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46206</v>
+      </c>
+      <c r="C13" s="14" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
+      <c r="D13" s="21"/>
+    </row>
+    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A14" s="7" t="s">
         <v>169</v>
-      </c>
-      <c r="B13" s="8">
-        <v>46192</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>171</v>
       </c>
       <c r="B14" s="8">
         <v>46192</v>
       </c>
       <c r="C14" s="6" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="B15" s="8">
+        <v>46192</v>
+      </c>
+      <c r="C15" s="6" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="15" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
+      <c r="A16" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B16" s="8">
         <v>46183</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="9" t="s">
+    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A17" s="9" t="s">
         <v>163</v>
-      </c>
-      <c r="B16" s="10">
-        <v>46164</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
-        <v>165</v>
       </c>
       <c r="B17" s="10">
         <v>46164</v>
       </c>
       <c r="C17" s="11" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A18" s="9" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="10">
+        <v>46164</v>
+      </c>
+      <c r="C18" s="11" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A19" s="9" t="s">
         <v>161</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B19" s="10">
         <v>46161</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="11" t="s">
         <v>162</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
-        <v>159</v>
-      </c>
-      <c r="B19" s="10">
-        <v>46142</v>
-      </c>
-      <c r="C19" s="11" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
+        <v>159</v>
+      </c>
+      <c r="B20" s="10">
+        <v>46142</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>157</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B21" s="10">
         <v>46129</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="11" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="9" t="s">
         <v>155</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B22" s="10">
         <v>46120</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="11" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="9" t="s">
         <v>153</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B23" s="10">
         <v>46063</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="11" t="s">
         <v>154</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
-        <v>149</v>
-      </c>
-      <c r="B23" s="10">
-        <v>46030</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>150</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
+        <v>149</v>
+      </c>
+      <c r="B24" s="10">
+        <v>46030</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="9" t="s">
         <v>151</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B25" s="10">
         <v>46024</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C25" s="11" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1996,7 +2043,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
       </c>

--- a/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
+++ b/backend/PDF_DOC/CBIC/Notifications/Anti-Dumping Duty/Anti-Dumping Duty Notifications.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76921ED1-72D8-406B-89AB-E70A077B1ABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEC218B8-0C49-40E0-9857-F57F9EB56BB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="191">
   <si>
     <t>Anti-Dumping Duty : 2026</t>
   </si>
@@ -589,6 +589,12 @@
   </si>
   <si>
     <t>Seeks to continue anti dumping duty on imports of “Phthalic Anhydride” originating in or exported from China PR and Korea RP for a further period of 5 years pursuant to sunset review by DGTR.</t>
+  </si>
+  <si>
+    <t>21/2026-Customs (ADD)</t>
+  </si>
+  <si>
+    <t>Seeks to continue applicability of anti-dumping duty on imports of Natural Mica based Pearl Industrial Pigments excluding cosmetic grade originating in or exported from China PR till 25th February, 2027.</t>
   </si>
 </sst>
 </file>
@@ -620,7 +626,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -629,37 +635,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.499984740745262"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC884F2"/>
+        <fgColor rgb="FFCCCCFF"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -676,7 +652,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -687,15 +663,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -705,27 +672,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="15" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="15" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="15" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -736,6 +685,7 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCCCCFF"/>
       <color rgb="FFC884F2"/>
     </mruColors>
   </colors>
@@ -1013,20 +963,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="18.5703125" customWidth="1"/>
-    <col min="3" max="3" width="155.5703125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="18.5546875" customWidth="1"/>
+    <col min="3" max="3" width="155.5546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1037,231 +987,234 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>189</v>
+      </c>
+      <c r="B6" s="10">
+        <v>46255</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>187</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B7" s="3">
         <v>46239</v>
       </c>
-      <c r="C6" s="24" t="s">
+      <c r="C7" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="D6" s="21"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>185</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B8" s="3">
         <v>46234</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C8" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="D7" s="21"/>
-    </row>
-    <row r="8" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+    </row>
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>183</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B9" s="3">
         <v>46230</v>
       </c>
-      <c r="C8" s="17" t="s">
+      <c r="C9" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="D8" s="21"/>
-    </row>
-    <row r="9" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="12" t="s">
+    </row>
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B9" s="13">
+      <c r="B10" s="3">
         <v>46213</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C10" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D9" s="21"/>
-    </row>
-    <row r="10" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A10" s="12" t="s">
+    </row>
+    <row r="11" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="13">
+      <c r="B11" s="3">
         <v>46209</v>
       </c>
-      <c r="C10" s="14" t="s">
+      <c r="C11" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="D10" s="21"/>
-    </row>
-    <row r="11" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A11" s="12" t="s">
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="B11" s="13">
+      <c r="B12" s="3">
         <v>46206</v>
       </c>
-      <c r="C11" s="14" t="s">
+      <c r="C12" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="D11" s="21"/>
-    </row>
-    <row r="12" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A12" s="12" t="s">
+    </row>
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="13">
+      <c r="B13" s="3">
         <v>46206</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C13" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="D12" s="21"/>
-    </row>
-    <row r="13" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="12" t="s">
+    </row>
+    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="B13" s="13">
+      <c r="B14" s="3">
         <v>46206</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C14" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="D13" s="21"/>
-    </row>
-    <row r="14" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="15" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="B14" s="8">
+      <c r="B15" s="7">
         <v>46192</v>
       </c>
-      <c r="C14" s="6" t="s">
+      <c r="C15" s="8" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="B15" s="8">
+      <c r="B16" s="7">
         <v>46192</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C16" s="8" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="30" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+    <row r="17" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A17" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="B16" s="8">
+      <c r="B17" s="7">
         <v>46183</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C17" s="8" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A17" s="9" t="s">
+    <row r="18" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B18" s="7">
         <v>46164</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="8" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B19" s="7">
         <v>46164</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C19" s="8" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A19" s="9" t="s">
+    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B20" s="7">
         <v>46161</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C20" s="8" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A20" s="9" t="s">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A21" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B21" s="7">
         <v>46142</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C21" s="8" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A21" s="9" t="s">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A22" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B22" s="7">
         <v>46129</v>
       </c>
-      <c r="C21" s="11" t="s">
+      <c r="C22" s="8" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="9" t="s">
+    <row r="23" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B23" s="7">
         <v>46120</v>
       </c>
-      <c r="C22" s="11" t="s">
+      <c r="C23" s="8" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A23" s="9" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A24" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B24" s="7">
         <v>46063</v>
       </c>
-      <c r="C23" s="11" t="s">
+      <c r="C24" s="8" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="9" t="s">
+    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A25" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B25" s="7">
         <v>46030</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C25" s="8" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="9" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B26" s="7">
         <v>46024</v>
       </c>
-      <c r="C25" s="11" t="s">
+      <c r="C26" s="8" t="s">
         <v>152</v>
       </c>
     </row>
@@ -1274,19 +1227,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A798CD2F-C939-4EB9-AF2B-731DD337AC51}">
   <dimension ref="A1:C48"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" customWidth="1"/>
-    <col min="3" max="3" width="136.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="3" max="3" width="136.5546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1297,7 +1250,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>65</v>
       </c>
@@ -1308,7 +1261,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>67</v>
       </c>
@@ -1319,7 +1272,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>69</v>
       </c>
@@ -1330,7 +1283,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>71</v>
       </c>
@@ -1341,7 +1294,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>73</v>
       </c>
@@ -1352,7 +1305,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>75</v>
       </c>
@@ -1363,7 +1316,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>77</v>
       </c>
@@ -1374,7 +1327,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="13" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>79</v>
       </c>
@@ -1385,7 +1338,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>81</v>
       </c>
@@ -1396,7 +1349,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>83</v>
       </c>
@@ -1407,7 +1360,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="16" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>85</v>
       </c>
@@ -1418,7 +1371,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>87</v>
       </c>
@@ -1429,7 +1382,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>89</v>
       </c>
@@ -1440,7 +1393,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>91</v>
       </c>
@@ -1451,7 +1404,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>93</v>
       </c>
@@ -1462,7 +1415,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -1473,7 +1426,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>97</v>
       </c>
@@ -1484,7 +1437,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>99</v>
       </c>
@@ -1495,7 +1448,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>101</v>
       </c>
@@ -1506,7 +1459,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>103</v>
       </c>
@@ -1517,7 +1470,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>105</v>
       </c>
@@ -1528,7 +1481,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>107</v>
       </c>
@@ -1539,7 +1492,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A28" s="4" t="s">
         <v>109</v>
       </c>
@@ -1550,7 +1503,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>110</v>
       </c>
@@ -1561,7 +1514,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>112</v>
       </c>
@@ -1572,7 +1525,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="60" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A31" s="4" t="s">
         <v>114</v>
       </c>
@@ -1583,7 +1536,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>115</v>
       </c>
@@ -1594,7 +1547,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>117</v>
       </c>
@@ -1605,7 +1558,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>119</v>
       </c>
@@ -1616,7 +1569,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>121</v>
       </c>
@@ -1627,7 +1580,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>123</v>
       </c>
@@ -1638,7 +1591,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>125</v>
       </c>
@@ -1649,7 +1602,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="38" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>127</v>
       </c>
@@ -1660,7 +1613,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>129</v>
       </c>
@@ -1671,7 +1624,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>131</v>
       </c>
@@ -1682,7 +1635,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>133</v>
       </c>
@@ -1693,7 +1646,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>135</v>
       </c>
@@ -1704,7 +1657,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>137</v>
       </c>
@@ -1715,7 +1668,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>139</v>
       </c>
@@ -1726,7 +1679,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>141</v>
       </c>
@@ -1737,7 +1690,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>143</v>
       </c>
@@ -1748,7 +1701,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>145</v>
       </c>
@@ -1759,7 +1712,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>147</v>
       </c>
@@ -1778,19 +1731,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4796F69-9381-4823-B7C2-88E9B5820315}">
   <dimension ref="A1:C36"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
-    <col min="2" max="2" width="16.140625" customWidth="1"/>
-    <col min="3" max="3" width="146.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="16.109375" customWidth="1"/>
+    <col min="3" max="3" width="146.5546875" style="4" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" ht="25.8" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
@@ -1801,7 +1754,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -1812,7 +1765,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -1823,7 +1776,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1834,7 +1787,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>12</v>
       </c>
@@ -1845,7 +1798,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="10" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>13</v>
       </c>
@@ -1856,7 +1809,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1867,7 +1820,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>16</v>
       </c>
@@ -1878,7 +1831,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -1889,7 +1842,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>20</v>
       </c>
@@ -1900,7 +1853,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>22</v>
       </c>
@@ -1911,7 +1864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>24</v>
       </c>
@@ -1922,7 +1875,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>26</v>
       </c>
@@ -1933,7 +1886,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="18" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>28</v>
       </c>
@@ -1944,7 +1897,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>30</v>
       </c>
@@ -1955,7 +1908,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>32</v>
       </c>
@@ -1966,7 +1919,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="21" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>34</v>
       </c>
@@ -1977,7 +1930,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>36</v>
       </c>
@@ -1988,7 +1941,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>38</v>
       </c>
@@ -1999,7 +1952,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -2010,7 +1963,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>42</v>
       </c>
@@ -2021,7 +1974,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>44</v>
       </c>
@@ -2032,7 +1985,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>46</v>
       </c>
@@ -2043,7 +1996,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>48</v>
       </c>
@@ -2054,7 +2007,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>50</v>
       </c>
@@ -2065,7 +2018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>52</v>
       </c>
@@ -2076,7 +2029,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="31" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>54</v>
       </c>
@@ -2087,7 +2040,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>56</v>
       </c>
@@ -2098,7 +2051,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>58</v>
       </c>
@@ -2109,7 +2062,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>60</v>
       </c>
@@ -2120,7 +2073,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>62</v>
       </c>
@@ -2131,7 +2084,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="45" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A36" s="4" t="s">
         <v>64</v>
       </c>
